--- a/data/medicina/misiones.xlsx
+++ b/data/medicina/misiones.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p5, p3</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p1, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p5, p1</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>p5, p4</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p4, p2</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p4</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5202,12 +5202,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>p5, p4</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>p5, p3</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>p4</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>p3</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>p3</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>p1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>p1, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -5877,12 +5877,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>p5, p1</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
     </row>
@@ -6012,12 +6012,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -6039,12 +6039,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
     </row>
@@ -6066,12 +6066,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>p4</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>p5</t>
         </is>
       </c>
     </row>
@@ -6093,12 +6093,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
     </row>
@@ -6120,12 +6120,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
@@ -6147,12 +6147,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>p3, p1</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>p1, p4</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>p6, p5</t>
         </is>
       </c>
     </row>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p6, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p3, p5</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p5, p3</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>p4, p6</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p5, p4</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p1, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p4</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p6, p1</t>
+          <t>p1, p2</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>p5, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>p1, p5</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>p5, p1</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>p2, p6</t>
+          <t>p1, p3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>p6</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>p4, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>p2, p5</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p6, p5</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p3, p6</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>p5</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">

--- a/data/medicina/misiones.xlsx
+++ b/data/medicina/misiones.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Misiones'!$A$1:$H$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$E$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Matriz'!$A$1:$E$60</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Plan'!$A$1:$H$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -905,10 +905,10 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -922,7 +922,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1060,31 +1060,31 @@
         <v>46120</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>46107</v>
+        <v>46127</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corregir control y subir notas. — Control lógica 2</t>
+          <t>Construcción del certamen. — Certamen 1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1133,34 +1133,34 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46128</v>
+        <v>46107</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Construcción del certamen. — Certamen 1</t>
+          <t>Corregir control y subir notas. — Control lógica 2</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1209,10 +1209,10 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46123</v>
+        <v>46122</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1264,12 +1264,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1285,10 +1285,10 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46125</v>
+        <v>46124</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1437,10 +1437,10 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46130</v>
+        <v>46129</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1665,10 +1665,10 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2200,31 +2200,31 @@
         <v>46155</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>46142</v>
+        <v>46169</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2</t>
+          <t>Cada profesor propone preguntas para el certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2273,34 +2273,34 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>46170</v>
+        <v>46142</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cada profesor propone preguntas para el certamen. — Certamen 2</t>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2428,31 +2428,31 @@
         <v>46162</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>46149</v>
+        <v>46169</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3</t>
+          <t>Construcción del certamen. — Certamen 2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2501,34 +2501,34 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>46170</v>
+        <v>46149</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Construcción del certamen. — Certamen 2</t>
+          <t>Corregir control y subir notas. — Control Modelos y Derivadas 3</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2577,10 +2577,10 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2594,12 +2594,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p3, p4</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2653,10 +2653,10 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p1</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2822,12 +2822,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2881,10 +2881,10 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B64" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2898,12 +2898,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3109,10 +3109,10 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="B70" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3489,10 +3489,10 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B80" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p4, p3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3527,19 +3527,19 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B81" s="3" t="n">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>construir_control</t>
+          <t>pedir_preguntas</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Construcción del certamen. — Certamen 3</t>
+          <t>Preguntas para examen. — Examen 1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3568,16 +3568,16 @@
         <v>46198</v>
       </c>
       <c r="B82" s="3" t="n">
-        <v>46219</v>
+        <v>46205</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>construir_control</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — Virgen del Carmen</t>
+          <t>Construcción del certamen. — Certamen 3</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3641,10 +3641,10 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="B84" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -3658,12 +3658,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3696,12 +3696,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p4, p2</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3793,10 +3793,10 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="B88" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3945,10 +3945,10 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B92" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -3962,17 +3962,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p2</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Construcción del examen. — Virgen del Carmen</t>
+          <t>Construcción del examen. — Examen 1</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3983,10 +3983,10 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B93" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4097,10 +4097,10 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4114,12 +4114,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4152,12 +4152,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4249,10 +4249,10 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -4266,17 +4266,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>p1, p4</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pauta del examen. — Virgen del Carmen</t>
+          <t>Pauta del examen. — Examen 1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4287,10 +4287,10 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B101" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -4304,12 +4304,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>p2, p1</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p3, p1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4401,10 +4401,10 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4418,12 +4418,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4439,19 +4439,19 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46205</v>
+        <v>46225</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Certamen</t>
+          <t>Examen</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>corregir_y_notas</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Corregir certamen y subir notas. — Certamen 3</t>
+          <t>Pauta del examen. — Examen 2</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4480,16 +4480,16 @@
         <v>46219</v>
       </c>
       <c r="B106" s="3" t="n">
-        <v>46226</v>
+        <v>46205</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Examen</t>
+          <t>Certamen</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>corregir_y_notas</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pauta del examen. — Examen 2</t>
+          <t>Corregir certamen y subir notas. — Certamen 3</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4553,10 +4553,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -4570,17 +4570,17 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p3</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corregir examen. — Virgen del Carmen</t>
+          <t>Corregir examen. — Examen 1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4629,10 +4629,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B110" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -4646,12 +4646,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sección 1</t>
+          <t>Sección 2</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>p4</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sección 2</t>
+          <t>Sección 1</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4715,7 +4715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -6007,17 +6007,13 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Construcción del examen. — Examen 2</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>p2, p3</t>
-        </is>
-      </c>
+          <t>Construcción del examen. — Examen 1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>p3, p2</t>
         </is>
       </c>
     </row>
@@ -6034,17 +6030,17 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Construcción del examen. — Virgen del Carmen</t>
+          <t>Construcción del examen. — Examen 2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>p2, p3</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>p2, p1</t>
         </is>
       </c>
     </row>
@@ -6056,24 +6052,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>corregir_examen</t>
+          <t>construir_examen</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Corregir examen. — Examen 2</t>
+          <t>Construcción del examen. — Virgen del Carmen</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>p2</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>p4</t>
-        </is>
-      </c>
+          <t>p1, p4</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6088,14 +6080,10 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Corregir examen. — Virgen del Carmen</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>p2</t>
-        </is>
-      </c>
+          <t>Corregir examen. — Examen 1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>p3</t>
@@ -6110,22 +6098,22 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>corregir_examen</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pauta del examen. — Examen 2</t>
+          <t>Corregir examen. — Examen 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>p4</t>
         </is>
       </c>
     </row>
@@ -6137,24 +6125,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pauta_examen</t>
+          <t>corregir_examen</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Pauta del examen. — Virgen del Carmen</t>
+          <t>Corregir examen. — Virgen del Carmen</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>p3, p1</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>p1, p4</t>
-        </is>
-      </c>
+          <t>p2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6164,22 +6148,18 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — Examen 2</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Todos</t>
-        </is>
-      </c>
+          <t>Pauta del examen. — Examen 1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p1, p4</t>
         </is>
       </c>
     </row>
@@ -6191,54 +6171,150 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pedir_preguntas</t>
+          <t>pauta_examen</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — Virgen del Carmen</t>
+          <t>Pauta del examen. — Examen 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p4, p1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>p4, p1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>pauta_examen</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Pauta del examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>p3, p1</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Examen 1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Examen 2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Examen</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>pedir_preguntas</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Preguntas para examen. — Virgen del Carmen</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Trabajo práctico</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>revisar_tp</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>Revisar TP y subir nota. — Trabajo Práctico</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Todos</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E56"/>
+  <autoFilter ref="A1:E60"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6420,10 +6496,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -6458,10 +6534,10 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -6496,10 +6572,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
-        <v>46191</v>
+        <v>46190</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -6648,10 +6724,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46121</v>
+        <v>46120</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -6686,10 +6762,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -6724,10 +6800,10 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -6876,10 +6952,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46123</v>
+        <v>46122</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -6914,10 +6990,10 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -6952,10 +7028,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -7104,10 +7180,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46125</v>
+        <v>46124</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -7142,10 +7218,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46167</v>
+        <v>46166</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -7180,10 +7256,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46202</v>
+        <v>46201</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -7332,10 +7408,10 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46130</v>
+        <v>46129</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -7370,10 +7446,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46172</v>
+        <v>46171</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -7408,10 +7484,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46207</v>
+        <v>46206</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -7560,10 +7636,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46142</v>
+        <v>46141</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>46128</v>
+        <v>46127</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -7598,10 +7674,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46184</v>
+        <v>46183</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>46170</v>
+        <v>46169</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -7636,10 +7712,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -9878,10 +9954,10 @@
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46198</v>
+        <v>46197</v>
       </c>
       <c r="B96" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -9905,7 +9981,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Preguntas para examen. — Virgen del Carmen</t>
+          <t>Preguntas para examen. — Examen 1</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -9916,10 +9992,10 @@
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B97" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10030,10 +10106,10 @@
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B100" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10057,7 +10133,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Construcción del examen. — Virgen del Carmen</t>
+          <t>Construcción del examen. — Examen 1</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10068,10 +10144,10 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B101" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10182,10 +10258,10 @@
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B104" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -10209,7 +10285,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pauta del examen. — Virgen del Carmen</t>
+          <t>Pauta del examen. — Examen 1</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -10220,10 +10296,10 @@
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B105" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -10334,10 +10410,10 @@
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="B108" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -10361,7 +10437,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Corregir examen. — Virgen del Carmen</t>
+          <t>Corregir examen. — Examen 1</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -10372,10 +10448,10 @@
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46240</v>
+        <v>46239</v>
       </c>
       <c r="B109" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>

--- a/data/medicina/misiones.xlsx
+++ b/data/medicina/misiones.xlsx
@@ -547,7 +547,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>RL, JCS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, CC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -623,7 +623,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>AR, IG</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>AR, DH</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>VB, SM</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>DH, EG</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>GM, NV</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, TY</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>JCS, JM</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, AR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>SM, IG</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>GM, CC</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, NV</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1573,7 +1573,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>SM, CC</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, RL</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1649,7 +1649,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, RL</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>TY, AR</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>NV, JCS</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>VB, JM</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, AR</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>NV, GM</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, EG</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>EG, JCS</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2143,7 +2143,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>IG, SM</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2295,7 +2295,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>JCS, GM</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>RL, SM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>RL, JM</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>CC, RL</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>GM, TY</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -3017,7 +3017,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>GM, DH</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>JCS, SM</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, JM</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>IG, VB</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, EG</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>DH, JCS</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>TY, CC</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>NV, DH</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>TY, VB</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, NV</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>SM, NV</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>CC, GM</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>EG, IG</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -4119,7 +4119,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>RL, AR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, VB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>GM, IG</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4385,7 +4385,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>NV, JM</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JM, JCS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -4499,7 +4499,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JCS, RL</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4689,7 +4689,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -4770,12 +4770,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, AR</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>JCS, JM</t>
         </is>
       </c>
     </row>
@@ -4797,12 +4797,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>RL, SM</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>JCS, GM</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>TY, VB</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>NV, DH</t>
         </is>
       </c>
     </row>
@@ -4851,12 +4851,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4878,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -4905,12 +4905,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>TY</t>
         </is>
       </c>
     </row>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
     </row>
@@ -4959,12 +4959,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>VB</t>
         </is>
       </c>
     </row>
@@ -4986,12 +4986,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5013,12 +5013,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>GM, CC</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>SM, IG</t>
         </is>
       </c>
     </row>
@@ -5040,12 +5040,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>CC, RL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>RL, JM</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>SM, NV</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, NV</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
     </row>
@@ -5202,12 +5202,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5229,12 +5229,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>IG</t>
         </is>
       </c>
     </row>
@@ -5256,12 +5256,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, NV</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>SM, CC</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>TY, AR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>NV, JCS</t>
         </is>
       </c>
     </row>
@@ -5310,12 +5310,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>NV, GM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, EG</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>GM, TY</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>GM, DH</t>
         </is>
       </c>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>IG, VB</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, EG</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>RL, JCS</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, CC</t>
         </is>
       </c>
     </row>
@@ -5418,12 +5418,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>VB, SM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>DH, EG</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5445,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
     </row>
@@ -5472,12 +5472,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>DH</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5499,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>CC</t>
         </is>
       </c>
     </row>
@@ -5526,12 +5526,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
     </row>
@@ -5553,12 +5553,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5580,12 +5580,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
     </row>
@@ -5607,12 +5607,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
     </row>
@@ -5634,12 +5634,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>JM</t>
         </is>
       </c>
     </row>
@@ -5661,12 +5661,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
     </row>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
     </row>
@@ -5715,12 +5715,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5742,12 +5742,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -5796,12 +5796,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5823,12 +5823,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, RL</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, RL</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>VB, JM</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, AR</t>
         </is>
       </c>
     </row>
@@ -5877,12 +5877,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>EG, JCS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>IG, SM</t>
         </is>
       </c>
     </row>
@@ -5904,12 +5904,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>JCS, SM</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, JM</t>
         </is>
       </c>
     </row>
@@ -5931,12 +5931,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>DH, JCS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>TY, CC</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>AR, IG</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>AR, DH</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>GM, NV</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, TY</t>
         </is>
       </c>
     </row>
@@ -6013,7 +6013,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>CC, GM</t>
         </is>
       </c>
     </row>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>NV, JM</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, VB</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>EG, IG</t>
         </is>
       </c>
       <c r="E50" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>SM</t>
         </is>
       </c>
     </row>
@@ -6108,12 +6108,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>SM</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="E53" t="inlineStr"/>
@@ -6159,7 +6159,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>RL, AR</t>
         </is>
       </c>
     </row>
@@ -6181,12 +6181,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JCS, RL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JM, JCS</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>GM, IG</t>
         </is>
       </c>
       <c r="E56" t="inlineStr"/>
@@ -6632,7 +6632,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, AR</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>RL, SM</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>TY, VB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>JCS, JM</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>JCS, GM</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6822,7 +6822,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>NV, DH</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>GM, CC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>CC, RL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>SM, NV</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>SM, IG</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>RL, JM</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>JM, NV</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7164,7 +7164,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7240,7 +7240,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7354,7 +7354,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -7468,7 +7468,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7582,7 +7582,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7658,7 +7658,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7696,7 +7696,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>RL, JCS</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>VB, SM</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, NV</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>TY, AR</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>NV, GM</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>GM, TY</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -8000,7 +8000,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>IG, VB</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, CC</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>DH, EG</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>SM, CC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8152,7 +8152,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>NV, JCS</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, EG</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>p4, p2</t>
+          <t>GM, DH</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -8266,7 +8266,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, EG</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -8304,7 +8304,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>AR, IG</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>GM, NV</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>p2, p4</t>
+          <t>DH, RL</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>VB, JM</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>p3, p4</t>
+          <t>EG, JCS</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>JCS, SM</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -8532,7 +8532,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>DH, JCS</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -8570,7 +8570,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>p1, p2</t>
+          <t>AR, DH</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, TY</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>VB, RL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>IG, AR</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -8722,7 +8722,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>IG, SM</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>p1, p3</t>
+          <t>VB, JM</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -8798,7 +8798,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>p4, p3</t>
+          <t>TY, CC</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -8874,7 +8874,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>VB</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -8950,7 +8950,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -8988,7 +8988,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -9026,7 +9026,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -9064,7 +9064,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -9102,7 +9102,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -9178,7 +9178,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -9330,7 +9330,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -9368,7 +9368,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>JM</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -9482,7 +9482,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -9558,7 +9558,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>GM</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9710,7 +9710,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>DH</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>CC</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>RL</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -9862,7 +9862,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>EG, IG</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -10090,7 +10090,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>p2, p3</t>
+          <t>NV, JM</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>p3, p2</t>
+          <t>CC, GM</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>p2, p1</t>
+          <t>EG, VB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>p3, p1</t>
+          <t>GM, IG</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JCS, RL</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -10280,7 +10280,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>p1, p4</t>
+          <t>RL, AR</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -10318,7 +10318,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>p4, p1</t>
+          <t>JM, JCS</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -10394,7 +10394,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>p3</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>p4</t>
+          <t>SM</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">

--- a/data/medicina/misiones.xlsx
+++ b/data/medicina/misiones.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-04-16||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-04-02||2026-04-16||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-16||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-04-23||2026-04-16||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -2024,7 +2024,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2279,7 +2279,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-28||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-05-14||2026-05-28||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-06-04||2026-05-28||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-04||2026-05-28||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3128,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-07-02||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-18||2026-07-02||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3560,7 +3560,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-07-16||Virgen del Carmen||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-02||2026-07-16||Virgen del Carmen||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3959,7 +3959,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-09||2026-07-02||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-09||2026-07-02||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09||2026-07-23||Examen 2||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-09||2026-07-23||Examen 2||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4472,7 +4472,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-23||2026-07-16||Virgen del Carmen||Examen||corregir_examen||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-23||2026-07-16||Virgen del Carmen||Examen||corregir_examen||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4568,7 +4568,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-30||2026-07-23||Examen 2||Examen||corregir_examen||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-30||2026-07-23||Examen 2||Examen||corregir_examen||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4722,7 +4722,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
@@ -4834,7 +4834,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -4946,7 +4946,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
@@ -5058,7 +5058,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
@@ -5170,7 +5170,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
@@ -5433,12 +5433,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -5465,12 +5465,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6153,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -6217,12 +6217,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -6249,12 +6249,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6309,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6946,7 +6946,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -7717,7 +7717,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-04-01||2026-04-15||Certamen 1||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -7861,7 +7861,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-04-22||2026-04-15||Certamen 1||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -7894,7 +7894,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-04-16||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-04-02||2026-04-16||Certamen 1||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-16||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-04-23||2026-04-16||Certamen 1||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8437,7 +8437,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8485,7 +8485,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||XX</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>XX</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||XX</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||EG</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-05-13||2026-05-27||Certamen 2||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9094,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -9109,7 +9109,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-03||2026-05-27||Certamen 2||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -9157,7 +9157,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-28||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-05-14||2026-05-28||Certamen 2||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -9286,7 +9286,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -9301,7 +9301,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-06-04||2026-05-28||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-04||2026-05-28||Certamen 2||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -9382,7 +9382,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-11||2026-06-04||Trabajo Práctico||Trabajo práctico||revisar_tp||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10006,7 +10006,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-06-17||2026-07-01||Certamen 3||Certamen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10150,7 +10150,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -10165,7 +10165,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-08||2026-07-01||Certamen 3||Certamen||corregir_y_notas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10198,7 +10198,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-07-02||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-06-18||2026-07-02||Certamen 3||Certamen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10342,7 +10342,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-09||2026-07-02||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-09||2026-07-02||Certamen 3||Certamen||corregir_y_notas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -10405,7 +10405,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-01||2026-07-15||Examen 1||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-22||2026-07-15||Examen 1||Examen||corregir_examen||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10582,7 +10582,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -10597,7 +10597,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-07-16||Virgen del Carmen||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-02||2026-07-16||Virgen del Carmen||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10726,7 +10726,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -10741,7 +10741,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-23||2026-07-16||Virgen del Carmen||Examen||corregir_examen||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-23||2026-07-16||Virgen del Carmen||Examen||corregir_examen||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10774,7 +10774,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-08||2026-07-22||Examen 2||Examen||pedir_preguntas||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10918,7 +10918,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -10933,7 +10933,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 2||TY, JCS, AR, XX</t>
+          <t>2026-07-29||2026-07-22||Examen 2||Examen||corregir_examen||Sección 2||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -10981,7 +10981,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09||2026-07-23||Examen 2||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-09||2026-07-23||Examen 2||Examen||pedir_preguntas||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>TY, JCS, AR, XX</t>
+          <t>TY, JCS, AR, EG</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -11125,7 +11125,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-30||2026-07-23||Examen 2||Examen||corregir_examen||Sección 1||TY, JCS, AR, XX</t>
+          <t>2026-07-30||2026-07-23||Examen 2||Examen||corregir_examen||Sección 1||TY, JCS, AR, EG</t>
         </is>
       </c>
     </row>

--- a/data/medicina/misiones.xlsx
+++ b/data/medicina/misiones.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 2||TY</t>
+          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||JCS</t>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 2||JCS</t>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 2||TY</t>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 2||TY</t>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 2||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 2||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||AR</t>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 2||AR</t>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -1688,7 +1688,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||EG</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 2||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -1880,7 +1880,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 2||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -1976,7 +1976,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 2||TY</t>
+          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||EG</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||EG</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 2||TY</t>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 2||TY</t>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||JCS</t>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 2||JCS</t>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3032,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||AR</t>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 2||AR</t>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -3224,7 +3224,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -3320,7 +3320,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 2||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -3368,7 +3368,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 2||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 2||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3752,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 2||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5369,12 +5369,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5401,12 +5401,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5470,7 +5470,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5502,7 +5502,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5534,7 +5534,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5566,7 +5566,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5625,12 +5625,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5657,12 +5657,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5689,12 +5689,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5721,12 +5721,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5753,12 +5753,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5785,12 +5785,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5854,7 +5854,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5886,7 +5886,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -5913,12 +5913,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5945,12 +5945,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -5977,12 +5977,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -6506,12 +6506,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6536,12 +6536,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -6566,12 +6566,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
     </row>
@@ -6596,12 +6596,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -6626,7 +6626,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -6746,12 +6746,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
     </row>
@@ -6776,12 +6776,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
     </row>
@@ -6836,12 +6836,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>BALANCEADO</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
     </row>
@@ -7270,7 +7270,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -7285,7 +7285,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 2||TY</t>
+          <t>2026-03-19||2026-03-26||Control lógica 2||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7318,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 2||TY</t>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 2||TY</t>
+          <t>2026-04-02||2026-03-26||Control lógica 2||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||JCS</t>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -7477,7 +7477,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -7558,7 +7558,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -7573,7 +7573,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 2||JCS</t>
+          <t>2026-03-26||2026-04-02||Control lógica 3||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -7606,7 +7606,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -7621,7 +7621,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 2||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7654,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 2||JCS</t>
+          <t>2026-04-09||2026-04-02||Control lógica 3||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -8086,7 +8086,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||AR</t>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -8182,7 +8182,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -8245,7 +8245,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 2||AR</t>
+          <t>2026-04-23||2026-04-30||Control Modelos y Derivadas 2||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 2||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 2||AR</t>
+          <t>2026-05-07||2026-04-30||Control Modelos y Derivadas 2||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -8518,7 +8518,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8533,7 +8533,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||EG</t>
+          <t>2026-04-30||2026-05-07||Control Modelos y Derivadas 3||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -8566,7 +8566,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -8581,7 +8581,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||EG</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||EG</t>
+          <t>2026-05-14||2026-05-07||Control Modelos y Derivadas 3||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 2||TY</t>
+          <t>2026-05-07||2026-05-14||Control Modelos y Derivadas 4||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -8869,7 +8869,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 2||TY</t>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -8902,7 +8902,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>TY</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 2||TY</t>
+          <t>2026-05-21||2026-05-14||Control Modelos y Derivadas 4||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -9445,7 +9445,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||JCS</t>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -9493,7 +9493,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -9526,7 +9526,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -9541,7 +9541,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 1||EG</t>
         </is>
       </c>
     </row>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9589,7 +9589,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 2||JCS</t>
+          <t>2026-06-11||2026-06-18||Control Trigonometría y Vectores 2||Control||construir_control||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -9622,7 +9622,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9637,7 +9637,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 2||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||escanear||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>JCS</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 2||JCS</t>
+          <t>2026-06-25||2026-06-18||Control Trigonometría y Vectores 2||Control||corregir_y_notas||Sección 2||AR</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -9733,7 +9733,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||AR</t>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -9814,7 +9814,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>TY</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 1||TY</t>
         </is>
       </c>
     </row>
@@ -9862,7 +9862,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -9877,7 +9877,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 2||AR</t>
+          <t>2026-06-18||2026-06-25||Control Trigonometría y Vectores 3||Control||construir_control||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -9910,7 +9910,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -9925,7 +9925,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 2||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||escanear||Sección 2||JCS</t>
         </is>
       </c>
     </row>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>JCS</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 2||AR</t>
+          <t>2026-07-02||2026-06-25||Control Trigonometría y Vectores 3||Control||corregir_y_notas||Sección 2||JCS</t>
         </is>
       </c>
     </row>
